--- a/TIMES-NZ/v303/SubRES_TMPL/SubRES_NewTechs_COM.xlsx
+++ b/TIMES-NZ/v303/SubRES_TMPL/SubRES_NewTechs_COM.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P185"/>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C_EDU-SH-GHP-ELC</t>
+          <t>C_EDU-WH-AIRHP-ELC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C_EDU-WH-AIRHP-ELC</t>
+          <t>C_EDU-MPM-MPM-ELC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C_EDU-WH-GHP-ELC</t>
+          <t>C_EDU-MPM-MPM-H2R</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C_EDU-MPM-MPM-ELC</t>
+          <t>C_EDU-MPS-MPS-H2R</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C_EDU-MPM-MPM-H2R</t>
+          <t>C_HLTH-SH-Boiler-PLT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C_EDU-MPS-MPS-H2R</t>
+          <t>C_HLTH-SH-Boiler-ELC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C_EDU-SC-GHP-ELC</t>
+          <t>C_HLTH-SH-Boiler-BIM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C_HLTH-SH-Boiler-PLT</t>
+          <t>C_HLTH-SH-Boiler-H2R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C_HLTH-SH-Boiler-ELC</t>
+          <t>C_HLTH-WH-Boiler-WOD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C_HLTH-SH-Boiler-BIM</t>
+          <t>C_HLTH-WH-Boiler-PLT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C_HLTH-SH-Boiler-H2R</t>
+          <t>C_HLTH-WH-Boiler-ELC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-Boiler-WOD</t>
+          <t>C_HLTH-WH-Boiler-BIM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-Boiler-PLT</t>
+          <t>C_HLTH-WH-Boiler-H2R</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-Boiler-ELC</t>
+          <t>C_HLTH-PH-Boiler-WOD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-Boiler-BIM</t>
+          <t>C_HLTH-PH-Boiler-PLT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-Boiler-H2R</t>
+          <t>C_HLTH-PH-Boiler-BIM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C_HLTH-PH-Boiler-WOD</t>
+          <t>C_HLTH-PH-Boiler-H2R</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C_HLTH-PH-Boiler-PLT</t>
+          <t>C_HLTH-WH-AIRHP-ELC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C_HLTH-PH-Boiler-BIM</t>
+          <t>C_HLTH-MPM-MPM-ELC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>C_HLTH-PH-Boiler-H2R</t>
+          <t>C_HLTH-MPM-MPM-H2R</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C_HLTH-SH-GHP-ELC</t>
+          <t>C_HLTH-MPS-MPS-H2R</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-AIRHP-ELC</t>
+          <t>C_OFFC-SH-Boiler-WOD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-GHP-ELC</t>
+          <t>C_OFFC-SH-Boiler-PLT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C_HLTH-MPM-MPM-ELC</t>
+          <t>C_OFFC-SH-Boiler-ELC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C_HLTH-MPM-MPM-H2R</t>
+          <t>C_OFFC-SH-Boiler-BIM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C_HLTH-MPS-MPS-H2R</t>
+          <t>C_OFFC-SH-Boiler-H2R</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C_HLTH-SC-GHP-ELC</t>
+          <t>C_OFFC-WH-Boiler-WOD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-Boiler-WOD</t>
+          <t>C_OFFC-WH-Boiler-PLT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-Boiler-PLT</t>
+          <t>C_OFFC-WH-Boiler-ELC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-Boiler-ELC</t>
+          <t>C_OFFC-WH-Boiler-BIM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-Boiler-BIM</t>
+          <t>C_OFFC-WH-Boiler-H2R</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-Boiler-H2R</t>
+          <t>C_OFFC-MPM-MPM-ELC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-Boiler-WOD</t>
+          <t>C_OFFC-MPM-MPM-H2R</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-Boiler-PLT</t>
+          <t>C_OFFC-MPS-MPS-H2R</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-Boiler-ELC</t>
+          <t>C_WSR-CK-Induction-ELC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-Boiler-BIM</t>
+          <t>C_WSR-CK-CK-H2R</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-Boiler-H2R</t>
+          <t>C_WSR-CK-Ovens-H2R</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-GHP-ELC</t>
+          <t>C_WSR-SH-Boiler-WOD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-GHP-ELC</t>
+          <t>C_WSR-SH-Boiler-PLT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C_OFFC-MPM-MPM-ELC</t>
+          <t>C_WSR-SH-Boiler-ELC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C_OFFC-MPM-MPM-H2R</t>
+          <t>C_WSR-SH-Boiler-BIM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C_OFFC-MPS-MPS-H2R</t>
+          <t>C_WSR-SH-Boiler-H2R</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>C_OFFC-SC-GHP-ELC</t>
+          <t>C_WSR-WH-Boiler-WOD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C_WSR-CK-Induction-ELC</t>
+          <t>C_WSR-WH-Boiler-PLT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C_WSR-CK-CK-H2R</t>
+          <t>C_WSR-WH-Boiler-ELC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C_WSR-CK-Ovens-H2R</t>
+          <t>C_WSR-WH-Boiler-BIM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>C_WSR-SH-Boiler-WOD</t>
+          <t>C_WSR-WH-Boiler-H2R</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>C_WSR-SH-Boiler-PLT</t>
+          <t>C_WSR-WH-AirHP-ELC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>C_WSR-SH-Boiler-ELC</t>
+          <t>C_WSR-MPM-MPM-ELC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C_WSR-SH-Boiler-BIM</t>
+          <t>C_WSR-MPM-MPM-H2R</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>C_WSR-SH-Boiler-H2R</t>
+          <t>C_WSR-MPS-MPS-H2R</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>C_WSR-WH-Boiler-WOD</t>
+          <t>C_OTH-SH-Boiler-WOD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C_WSR-WH-Boiler-PLT</t>
+          <t>C_OTH-SH-Boiler-PLT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C_WSR-WH-Boiler-ELC</t>
+          <t>C_OTH-SH-Boiler-ELC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>C_WSR-WH-Boiler-BIM</t>
+          <t>C_OTH-SH-Boiler-BIM</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C_WSR-WH-Boiler-H2R</t>
+          <t>C_OTH-SH-Boiler-H2R</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C_WSR-SH-GHP-ELC</t>
+          <t>C_OTH-WH-Boiler-WOD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>C_WSR-WH-AirHP-ELC</t>
+          <t>C_OTH-WH-Boiler-PLT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>C_WSR-WH-GHP-ELC</t>
+          <t>C_OTH-WH-Boiler-ELC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>C_WSR-MPM-MPM-ELC</t>
+          <t>C_OTH-WH-Boiler-BIM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C_WSR-MPM-MPM-H2R</t>
+          <t>C_OTH-WH-Boiler-H2R</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C_WSR-MPS-MPS-H2R</t>
+          <t>C_OTH-WH-AirHP-ELC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>C_WSR-SC-GHP-ELC</t>
+          <t>C_OTH-MPM-MPM-ELC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C_OTH-SH-Boiler-WOD</t>
+          <t>C_OTH-MPM-MPM-H2R</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C_OTH-SH-Boiler-PLT</t>
+          <t>C_OTH-MPS-MPS-H2R</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2440,553 +2440,1311 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>DMD</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>C_OTH-SH-Boiler-ELC</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>GW</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>DAYNITE</t>
-        </is>
-      </c>
-    </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>DMD</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>C_OTH-SH-Boiler-BIM</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>GW</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>DAYNITE</t>
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>CommercialNewTechParameters</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>Defines technical parameters for future commercial technologies</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DMD</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>C_OTH-SH-Boiler-H2R</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>GW</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>DAYNITE</t>
+          <t>~FI_T</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>TechName</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>C_OTH-WH-Boiler-WOD</t>
+          <t>Comm-In</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>Comm-Out</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>START</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
+          <t>EFF</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>EFF~2030</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>EFF~2050</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>INVCOST</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>INVCOST~2030</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>INVCOST~2050</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>FIXOM</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>AF</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>FLO_MARK~2030</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>FLO_MARK~2050</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>FLO_MARK~0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-SH-Boiler-PLT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>C_OTH-WH-Boiler-PLT</t>
+          <t>COMPLT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-Boiler-SH</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v/>
+      </c>
+      <c r="G81" t="n">
+        <v/>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>6007.952913170731</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v/>
+      </c>
+      <c r="K81" t="n">
+        <v/>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>12.282926829268293</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-SH-Boiler-ELC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>C_OTH-WH-Boiler-ELC</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-Boiler-SH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v/>
+      </c>
+      <c r="G82" t="n">
+        <v/>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1550.8742770731708</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v/>
+      </c>
+      <c r="K82" t="n">
+        <v/>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-SH-Boiler-BIM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>C_OTH-WH-Boiler-BIM</t>
+          <t>COMBIM</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-Boiler-SH</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v/>
+      </c>
+      <c r="G83" t="n">
+        <v/>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1806.3124799999998</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v/>
+      </c>
+      <c r="K83" t="n">
+        <v/>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-SH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>C_OTH-WH-Boiler-H2R</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-Boiler-SH</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v/>
+      </c>
+      <c r="G84" t="n">
+        <v/>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2251.869509268293</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v/>
+      </c>
+      <c r="K84" t="n">
+        <v/>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-WH-Boiler-WOD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C_OTH-SH-GHP-ELC</t>
+          <t>COMWOD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-Boiler-WH</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
-        </is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v/>
+      </c>
+      <c r="G85" t="n">
+        <v/>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>6502.7264019512195</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v/>
+      </c>
+      <c r="K85" t="n">
+        <v/>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>12.282926829268293</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>0.216895</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v/>
+      </c>
+      <c r="O85" t="n">
+        <v/>
+      </c>
+      <c r="P85" t="n">
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-WH-Boiler-PLT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C_OTH-WH-AirHP-ELC</t>
+          <t>COMPLT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-Boiler-WH</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
-        </is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v/>
+      </c>
+      <c r="G86" t="n">
+        <v/>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>6007.952913170731</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v/>
+      </c>
+      <c r="K86" t="n">
+        <v/>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>12.282926829268293</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>0.216895</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v/>
+      </c>
+      <c r="O86" t="n">
+        <v/>
+      </c>
+      <c r="P86" t="n">
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-WH-Boiler-BIM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>C_OTH-WH-GHP-ELC</t>
+          <t>COMBIM</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-Boiler-WH</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v/>
+      </c>
+      <c r="G87" t="n">
+        <v/>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1806.3124799999998</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v/>
+      </c>
+      <c r="K87" t="n">
+        <v/>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>0.216895</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-WH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>C_OTH-MPM-MPM-ELC</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-Boiler-WH</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v/>
+      </c>
+      <c r="G88" t="n">
+        <v/>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2251.869509268293</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v/>
+      </c>
+      <c r="K88" t="n">
+        <v/>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>0.216895</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-WH-AIRHP-ELC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>C_OTH-MPM-MPM-H2R</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-WH</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1842.439024390244</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1750.3170731707316</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>1715.310731707317</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>0.216895</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-MPM-MPM-ELC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C_OTH-MPS-MPS-H2R</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-MPM</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v/>
+      </c>
+      <c r="G90" t="n">
+        <v/>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>232.01085375609756</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v/>
+      </c>
+      <c r="K90" t="n">
+        <v/>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-MPM-MPM-H2R</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>C_OTH-SC-GHP-ELC</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-MPM</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1075.9843902439025</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1022.1851707317073</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>1001.7414673170732</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>C_EDU-MPS-MPS-H2R</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C_DATA-SC-GHP-ELC</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>C_EDU-MPS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>DAYNITE</t>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1075.9843902439025</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1022.1851707317073</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>1001.7414673170732</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>0.216895</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>C_HLTH-SH-Boiler-PLT</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>COMPLT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>C_HLTH-Boiler-SH</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v/>
+      </c>
+      <c r="G93" t="n">
+        <v/>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2403.1816565853655</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v/>
+      </c>
+      <c r="K93" t="n">
+        <v/>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>12.282926829268293</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>0.342188</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
-        <is>
-          <t>CommercialNewTechParameters</t>
-        </is>
-      </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>Defines technical parameters for future commercial technologies</t>
-        </is>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>C_HLTH-SH-Boiler-ELC</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>COMELC</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>C_HLTH-Boiler-SH</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v/>
+      </c>
+      <c r="G94" t="n">
+        <v/>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>620.3498336585366</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v/>
+      </c>
+      <c r="K94" t="n">
+        <v/>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>0.342188</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v/>
+      </c>
+      <c r="O94" t="n">
+        <v/>
+      </c>
+      <c r="P94" t="n">
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>~FI_T</t>
+          <t>C_HLTH-SH-Boiler-BIM</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>COMBIM</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>C_HLTH-Boiler-SH</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v/>
+      </c>
+      <c r="G95" t="n">
+        <v/>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>722.5251148292683</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v/>
+      </c>
+      <c r="K95" t="n">
+        <v/>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>0.342188</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TechName</t>
+          <t>C_HLTH-SH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Comm-In</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Comm-Out</t>
+          <t>C_HLTH-Boiler-SH</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>START</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>EFF</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>EFF~2030</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>EFF~2050</t>
-        </is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v/>
+      </c>
+      <c r="G96" t="n">
+        <v/>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>INVCOST</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>INVCOST~2030</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>INVCOST~2050</t>
-        </is>
+          <t>900.7479265365854</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v/>
+      </c>
+      <c r="K96" t="n">
+        <v/>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>FIXOM</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>AF</t>
+          <t>0.342188</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>FLO_MARK~2030</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>FLO_MARK~2050</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>FLO_MARK~0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C_EDU-SH-Boiler-PLT</t>
+          <t>C_HLTH-WH-Boiler-WOD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>COMPLT</t>
+          <t>COMWOD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>C_EDU-SH</t>
+          <t>C_HLTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2996,7 +3754,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3012,7 +3770,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>6007.952913170731</t>
+          <t>2601.090315121951</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -3028,7 +3786,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.45625</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -3038,7 +3796,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -3050,17 +3808,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C_EDU-SH-Boiler-ELC</t>
+          <t>C_HLTH-WH-Boiler-PLT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMPLT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>C_EDU-SH</t>
+          <t>C_HLTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3070,7 +3828,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3086,7 +3844,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1550.8742770731708</t>
+          <t>2403.1816565853655</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -3097,22 +3855,22 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.45625</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -3124,17 +3882,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C_EDU-SH-Boiler-BIM</t>
+          <t>C_HLTH-WH-Boiler-ELC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>COMBIM</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>C_EDU-SH</t>
+          <t>C_HLTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3144,7 +3902,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3155,12 +3913,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1806.3124799999998</t>
+          <t>620.3498336585366</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -3176,39 +3934,33 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.45625</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v/>
+      </c>
+      <c r="O99" t="n">
+        <v/>
+      </c>
+      <c r="P99" t="n">
+        <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C_EDU-SH-Boiler-H2R</t>
+          <t>C_HLTH-WH-Boiler-BIM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>COMH2R</t>
+          <t>COMBIM</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>C_EDU-SH</t>
+          <t>C_HLTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3218,7 +3970,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3234,7 +3986,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2251.869509268293</t>
+          <t>722.5251148292683</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -3250,7 +4002,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.45625</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -3272,17 +4024,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C_EDU-WH-Boiler-WOD</t>
+          <t>C_HLTH-WH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COMWOD</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>C_EDU-WH</t>
+          <t>C_HLTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3292,7 +4044,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3303,12 +4055,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>6502.7264019512195</t>
+          <t>900.7479265365854</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -3319,38 +4071,44 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>12.282926829268293</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>0.216895</t>
-        </is>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
+          <t>0.45625</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>C_EDU-WH-Boiler-PLT</t>
+          <t>C_HLTH-PH-Boiler-WOD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>COMPLT</t>
+          <t>COMWOD</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>C_EDU-WH</t>
+          <t>C_HLTH-Boiler-PH</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3360,7 +4118,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3376,7 +4134,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>6007.952913170731</t>
+          <t>2601.090315121951</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -3392,33 +4150,39 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>0.216895</t>
-        </is>
-      </c>
-      <c r="N102" t="n">
-        <v/>
-      </c>
-      <c r="O102" t="n">
-        <v/>
-      </c>
-      <c r="P102" t="n">
-        <v/>
+          <t>0.45625</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>C_EDU-WH-Boiler-BIM</t>
+          <t>C_HLTH-PH-Boiler-PLT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>COMBIM</t>
+          <t>COMPLT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>C_EDU-WH</t>
+          <t>C_HLTH-Boiler-PH</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3428,7 +4192,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3439,12 +4203,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1806.3124799999998</t>
+          <t>2403.1816565853655</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -3455,22 +4219,22 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>0.216895</t>
+          <t>0.45625</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -3482,17 +4246,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>C_EDU-WH-Boiler-H2R</t>
+          <t>C_HLTH-PH-Boiler-BIM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>COMH2R</t>
+          <t>COMBIM</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>C_EDU-WH</t>
+          <t>C_HLTH-Boiler-PH</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3502,7 +4266,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3518,7 +4282,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2251.869509268293</t>
+          <t>722.5251148292683</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -3534,17 +4298,17 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>0.216895</t>
+          <t>0.45625</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -3556,17 +4320,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>C_EDU-SH-GHP-ELC</t>
+          <t>C_HLTH-PH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>C_EDU-SH</t>
+          <t>C_HLTH-Boiler-PH</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3576,57 +4340,49 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v/>
+      </c>
+      <c r="G105" t="n">
+        <v/>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2267.428292682927</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>2154.0568780487806</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>2110.9757404878046</t>
-        </is>
+          <t>900.7479265365854</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v/>
+      </c>
+      <c r="K105" t="n">
+        <v/>
       </c>
       <c r="L105" t="inlineStr">
         <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>0.45625</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -3638,7 +4394,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>C_EDU-WH-AIRHP-ELC</t>
+          <t>C_HLTH-WH-AIRHP-ELC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3648,7 +4404,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>C_EDU-WH</t>
+          <t>C_HLTH-WH</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3698,7 +4454,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>0.216895</t>
+          <t>0.45625</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -3720,7 +4476,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>C_EDU-WH-GHP-ELC</t>
+          <t>C_HLTH-MPM-MPM-ELC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3730,7 +4486,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>C_EDU-WH</t>
+          <t>C_HLTH-MPM</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3740,38 +4496,30 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v/>
+      </c>
+      <c r="G107" t="n">
+        <v/>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2267.428292682927</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>2154.0568780487806</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>2110.9757404878046</t>
-        </is>
+          <t>232.01085375609756</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v/>
+      </c>
+      <c r="K107" t="n">
+        <v/>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -3780,12 +4528,12 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>0.216895</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -3802,17 +4550,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C_EDU-MPM-MPM-ELC</t>
+          <t>C_HLTH-MPM-MPM-H2R</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>C_EDU-MPM</t>
+          <t>C_HLTH-MPM</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3822,14 +4570,18 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v/>
-      </c>
-      <c r="G108" t="n">
-        <v/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3838,18 +4590,22 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>232.01085375609756</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
-        <v/>
-      </c>
-      <c r="K108" t="n">
-        <v/>
+          <t>1075.9843902439025</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>1022.1851707317073</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>1001.7414673170732</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -3859,12 +4615,12 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
           <t>0.5</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>1.0</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -3876,7 +4632,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>C_EDU-MPM-MPM-H2R</t>
+          <t>C_HLTH-MPS-MPS-H2R</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3886,7 +4642,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>C_EDU-MPM</t>
+          <t>C_HLTH-MPS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3936,39 +4692,33 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.45625</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v/>
+      </c>
+      <c r="O109" t="n">
+        <v/>
+      </c>
+      <c r="P109" t="n">
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>C_EDU-MPS-MPS-H2R</t>
+          <t>C_OFFC-SH-Boiler-WOD</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>COMH2R</t>
+          <t>COMWOD</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>C_EDU-MPS</t>
+          <t>C_OFFC-Boiler-SH</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3978,47 +4728,39 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v/>
+      </c>
+      <c r="G110" t="n">
+        <v/>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1075.9843902439025</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>1022.1851707317073</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>1001.7414673170732</t>
-        </is>
+          <t>1300.545771707317</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v/>
+      </c>
+      <c r="K110" t="n">
+        <v/>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>0.216895</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -4040,17 +4782,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C_EDU-SC-GHP-ELC</t>
+          <t>C_OFFC-SH-Boiler-PLT</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMPLT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>C_EDU-SC</t>
+          <t>C_OFFC-Boiler-SH</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4060,73 +4802,71 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v/>
+      </c>
+      <c r="G111" t="n">
+        <v/>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1316.0284009756099</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>1250.2263053658537</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>1225.2219512195122</t>
-        </is>
+          <t>1201.5907054634147</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v/>
+      </c>
+      <c r="K111" t="n">
+        <v/>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>0.108447</t>
-        </is>
-      </c>
-      <c r="N111" t="n">
-        <v/>
-      </c>
-      <c r="O111" t="n">
-        <v/>
-      </c>
-      <c r="P111" t="n">
-        <v/>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C_HLTH-SH-Boiler-PLT</t>
+          <t>C_OFFC-SH-Boiler-ELC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>COMPLT</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_OFFC-Boiler-SH</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4136,7 +4876,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -4152,7 +4892,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2403.1816565853655</t>
+          <t>310.17497824390244</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -4163,44 +4903,38 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>12.282926829268293</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>0.342188</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v/>
+      </c>
+      <c r="O112" t="n">
+        <v/>
+      </c>
+      <c r="P112" t="n">
+        <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C_HLTH-SH-Boiler-ELC</t>
+          <t>C_OFFC-SH-Boiler-BIM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMBIM</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_OFFC-Boiler-SH</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4210,7 +4944,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -4221,12 +4955,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>620.3498336585366</t>
+          <t>361.262496</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -4242,33 +4976,39 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>0.342188</t>
-        </is>
-      </c>
-      <c r="N113" t="n">
-        <v/>
-      </c>
-      <c r="O113" t="n">
-        <v/>
-      </c>
-      <c r="P113" t="n">
-        <v/>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C_HLTH-SH-Boiler-BIM</t>
+          <t>C_OFFC-SH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>COMBIM</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_OFFC-Boiler-SH</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4278,7 +5018,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -4294,7 +5034,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>722.5251148292683</t>
+          <t>450.3740246829268</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -4310,7 +5050,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>0.342188</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -4332,17 +5072,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C_HLTH-SH-Boiler-H2R</t>
+          <t>C_OFFC-WH-Boiler-WOD</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>COMH2R</t>
+          <t>COMWOD</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_OFFC-Boiler-WH</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4352,7 +5092,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -4363,12 +5103,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>900.7479265365854</t>
+          <t>1300.545771707317</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -4379,22 +5119,22 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>0.342188</t>
+          <t>0.447543</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -4406,17 +5146,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-Boiler-WOD</t>
+          <t>C_OFFC-WH-Boiler-PLT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>COMWOD</t>
+          <t>COMPLT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>C_HLTH-WH</t>
+          <t>C_OFFC-Boiler-WH</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4426,7 +5166,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -4442,7 +5182,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2601.090315121951</t>
+          <t>1201.5907054634147</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -4458,17 +5198,17 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>0.45625</t>
+          <t>0.447543</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -4480,17 +5220,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-Boiler-PLT</t>
+          <t>C_OFFC-WH-Boiler-ELC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>COMPLT</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>C_HLTH-WH</t>
+          <t>C_OFFC-Boiler-WH</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4500,7 +5240,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -4516,7 +5256,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2403.1816565853655</t>
+          <t>310.17497824390244</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -4527,44 +5267,38 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>12.282926829268293</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>0.45625</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.447543</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v/>
+      </c>
+      <c r="O117" t="n">
+        <v/>
+      </c>
+      <c r="P117" t="n">
+        <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-Boiler-ELC</t>
+          <t>C_OFFC-WH-Boiler-BIM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMBIM</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>C_HLTH-WH</t>
+          <t>C_OFFC-Boiler-WH</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4574,7 +5308,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -4585,12 +5319,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>620.3498336585366</t>
+          <t>361.262496</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -4606,33 +5340,39 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>0.45625</t>
-        </is>
-      </c>
-      <c r="N118" t="n">
-        <v/>
-      </c>
-      <c r="O118" t="n">
-        <v/>
-      </c>
-      <c r="P118" t="n">
-        <v/>
+          <t>0.447543</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-Boiler-BIM</t>
+          <t>C_OFFC-WH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>COMBIM</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>C_HLTH-WH</t>
+          <t>C_OFFC-Boiler-WH</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4642,7 +5382,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -4658,7 +5398,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>722.5251148292683</t>
+          <t>450.3740246829268</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -4674,7 +5414,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>0.45625</t>
+          <t>0.447543</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -4696,17 +5436,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-Boiler-H2R</t>
+          <t>C_OFFC-MPM-MPM-ELC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>COMH2R</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>C_HLTH-WH</t>
+          <t>C_OFFC-MPM</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4716,7 +5456,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4727,12 +5467,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>900.7479265365854</t>
+          <t>232.01085375609756</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -4743,44 +5483,38 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>0.45625</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v/>
+      </c>
+      <c r="O120" t="n">
+        <v/>
+      </c>
+      <c r="P120" t="n">
+        <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C_HLTH-PH-Boiler-WOD</t>
+          <t>C_OFFC-MPM-MPM-H2R</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>COMWOD</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>C_HLTH-PH</t>
+          <t>C_OFFC-MPM</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4790,49 +5524,57 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v/>
-      </c>
-      <c r="G121" t="n">
-        <v/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2601.090315121951</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
-        <v/>
-      </c>
-      <c r="K121" t="n">
-        <v/>
+          <t>1075.9843902439025</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>1022.1851707317073</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>1001.7414673170732</t>
+        </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>12.282926829268293</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>0.45625</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -4844,17 +5586,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>C_HLTH-PH-Boiler-PLT</t>
+          <t>C_OFFC-MPS-MPS-H2R</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>COMPLT</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>C_HLTH-PH</t>
+          <t>C_OFFC-MPS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4864,71 +5606,73 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v/>
-      </c>
-      <c r="G122" t="n">
-        <v/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2403.1816565853655</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
-        <v/>
-      </c>
-      <c r="K122" t="n">
-        <v/>
+          <t>1075.9843902439025</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>1022.1851707317073</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>1001.7414673170732</t>
+        </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>12.282926829268293</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>0.45625</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.447543</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v/>
+      </c>
+      <c r="O122" t="n">
+        <v/>
+      </c>
+      <c r="P122" t="n">
+        <v/>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>C_HLTH-PH-Boiler-BIM</t>
+          <t>C_WSR-CK-Induction-ELC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>COMBIM</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>C_HLTH-PH</t>
+          <t>C_WSR-CK</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4938,7 +5682,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -4949,12 +5693,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>722.5251148292683</t>
+          <t>811.5505401951219</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -4965,34 +5709,28 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>0.45625</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.483</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v/>
+      </c>
+      <c r="O123" t="n">
+        <v/>
+      </c>
+      <c r="P123" t="n">
+        <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>C_HLTH-PH-Boiler-H2R</t>
+          <t>C_WSR-CK-CK-H2R</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5002,7 +5740,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>C_HLTH-PH</t>
+          <t>C_WSR-CK</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5012,7 +5750,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -5023,12 +5761,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>900.7479265365854</t>
+          <t>1013.3414634146342</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -5039,44 +5777,38 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>0.45625</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.483</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v/>
+      </c>
+      <c r="O124" t="n">
+        <v/>
+      </c>
+      <c r="P124" t="n">
+        <v/>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>C_HLTH-SH-GHP-ELC</t>
+          <t>C_WSR-CK-Ovens-H2R</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_WSR-CK</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5086,18 +5818,14 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v/>
+      </c>
+      <c r="G125" t="n">
+        <v/>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -5106,18 +5834,14 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2267.428292682927</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>2154.0568780487806</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>2110.9757404878046</t>
-        </is>
+          <t>3373.710978536585</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v/>
+      </c>
+      <c r="K125" t="n">
+        <v/>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -5126,39 +5850,33 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>0.342188</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.483</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v/>
+      </c>
+      <c r="O125" t="n">
+        <v/>
+      </c>
+      <c r="P125" t="n">
+        <v/>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-AIRHP-ELC</t>
+          <t>C_WSR-SH-Boiler-WOD</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMWOD</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>C_HLTH-WH</t>
+          <t>C_WSR-Boiler-SH</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5168,57 +5886,49 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v/>
+      </c>
+      <c r="G126" t="n">
+        <v/>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1842.439024390244</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>1750.3170731707316</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>1715.310731707317</t>
-        </is>
+          <t>1300.545771707317</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v/>
+      </c>
+      <c r="K126" t="n">
+        <v/>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>0.45625</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -5230,17 +5940,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>C_HLTH-WH-GHP-ELC</t>
+          <t>C_WSR-SH-Boiler-PLT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMPLT</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>C_HLTH-WH</t>
+          <t>C_WSR-Boiler-SH</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5250,57 +5960,49 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v/>
+      </c>
+      <c r="G127" t="n">
+        <v/>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2267.428292682927</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>2154.0568780487806</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>2110.9757404878046</t>
-        </is>
+          <t>1201.5907054634147</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v/>
+      </c>
+      <c r="K127" t="n">
+        <v/>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>0.45625</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -5312,7 +6014,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>C_HLTH-MPM-MPM-ELC</t>
+          <t>C_WSR-SH-Boiler-ELC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5322,7 +6024,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>C_HLTH-MPM</t>
+          <t>C_WSR-Boiler-SH</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5343,12 +6045,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>232.01085375609756</t>
+          <t>310.17497824390244</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -5359,44 +6061,38 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v/>
+      </c>
+      <c r="O128" t="n">
+        <v/>
+      </c>
+      <c r="P128" t="n">
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>C_HLTH-MPM-MPM-H2R</t>
+          <t>C_WSR-SH-Boiler-BIM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>COMH2R</t>
+          <t>COMBIM</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>C_HLTH-MPM</t>
+          <t>C_WSR-Boiler-SH</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5406,38 +6102,30 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v/>
+      </c>
+      <c r="G129" t="n">
+        <v/>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1075.9843902439025</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>1022.1851707317073</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>1001.7414673170732</t>
-        </is>
+          <t>361.262496</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v/>
+      </c>
+      <c r="K129" t="n">
+        <v/>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -5446,17 +6134,17 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -5468,7 +6156,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>C_HLTH-MPS-MPS-H2R</t>
+          <t>C_WSR-SH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5478,7 +6166,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>C_HLTH-MPS</t>
+          <t>C_WSR-Boiler-SH</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5488,38 +6176,30 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v/>
+      </c>
+      <c r="G130" t="n">
+        <v/>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1075.9843902439025</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>1022.1851707317073</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>1001.7414673170732</t>
-        </is>
+          <t>450.3740246829268</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v/>
+      </c>
+      <c r="K130" t="n">
+        <v/>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -5528,33 +6208,39 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>0.45625</t>
-        </is>
-      </c>
-      <c r="N130" t="n">
-        <v/>
-      </c>
-      <c r="O130" t="n">
-        <v/>
-      </c>
-      <c r="P130" t="n">
-        <v/>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>C_HLTH-SC-GHP-ELC</t>
+          <t>C_WSR-WH-Boiler-WOD</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMWOD</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_WSR-Boiler-WH</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5564,73 +6250,71 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v/>
+      </c>
+      <c r="G131" t="n">
+        <v/>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1316.0284009756099</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>1250.2263053658537</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>1225.2219512195122</t>
-        </is>
+          <t>1300.545771707317</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v/>
+      </c>
+      <c r="K131" t="n">
+        <v/>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>0.228125</t>
-        </is>
-      </c>
-      <c r="N131" t="n">
-        <v/>
-      </c>
-      <c r="O131" t="n">
-        <v/>
-      </c>
-      <c r="P131" t="n">
-        <v/>
+          <t>0.483</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-Boiler-WOD</t>
+          <t>C_WSR-WH-Boiler-PLT</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>COMWOD</t>
+          <t>COMPLT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>C_OFFC-SH</t>
+          <t>C_WSR-Boiler-WH</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5640,7 +6324,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -5656,7 +6340,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1300.545771707317</t>
+          <t>1201.5907054634147</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -5672,17 +6356,17 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -5694,17 +6378,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-Boiler-PLT</t>
+          <t>C_WSR-WH-Boiler-ELC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>COMPLT</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>C_OFFC-SH</t>
+          <t>C_WSR-Boiler-WH</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5714,7 +6398,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -5730,7 +6414,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>1201.5907054634147</t>
+          <t>310.17497824390244</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -5741,44 +6425,38 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>12.282926829268293</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.483</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v/>
+      </c>
+      <c r="O133" t="n">
+        <v/>
+      </c>
+      <c r="P133" t="n">
+        <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-Boiler-ELC</t>
+          <t>C_WSR-WH-Boiler-BIM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMBIM</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>C_OFFC-SH</t>
+          <t>C_WSR-Boiler-WH</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5788,7 +6466,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -5799,12 +6477,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>310.17497824390244</t>
+          <t>361.262496</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -5820,33 +6498,39 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N134" t="n">
-        <v/>
-      </c>
-      <c r="O134" t="n">
-        <v/>
-      </c>
-      <c r="P134" t="n">
-        <v/>
+          <t>0.483</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-Boiler-BIM</t>
+          <t>C_WSR-WH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>COMBIM</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>C_OFFC-SH</t>
+          <t>C_WSR-Boiler-WH</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5856,7 +6540,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -5872,7 +6556,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>361.262496</t>
+          <t>450.3740246829268</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -5888,7 +6572,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -5910,17 +6594,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-Boiler-H2R</t>
+          <t>C_WSR-WH-AirHP-ELC</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>COMH2R</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>C_OFFC-SH</t>
+          <t>C_WSR-WH</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5930,71 +6614,73 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="F136" t="n">
-        <v/>
-      </c>
-      <c r="G136" t="n">
-        <v/>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>450.3740246829268</t>
-        </is>
-      </c>
-      <c r="J136" t="n">
-        <v/>
-      </c>
-      <c r="K136" t="n">
-        <v/>
+          <t>1842.439024390244</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>1750.3170731707316</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>1715.310731707317</t>
+        </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.483</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v/>
+      </c>
+      <c r="O136" t="n">
+        <v/>
+      </c>
+      <c r="P136" t="n">
+        <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-Boiler-WOD</t>
+          <t>C_WSR-MPM-MPM-ELC</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>COMWOD</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>C_OFFC-WH</t>
+          <t>C_WSR-MPM</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6004,7 +6690,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -6015,12 +6701,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1300.545771707317</t>
+          <t>232.01085375609756</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -6031,44 +6717,38 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>12.282926829268293</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>0.447543</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>0.483</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v/>
+      </c>
+      <c r="O137" t="n">
+        <v/>
+      </c>
+      <c r="P137" t="n">
+        <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-Boiler-PLT</t>
+          <t>C_WSR-MPM-MPM-H2R</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>COMPLT</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>C_OFFC-WH</t>
+          <t>C_WSR-MPM</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6078,39 +6758,47 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="F138" t="n">
-        <v/>
-      </c>
-      <c r="G138" t="n">
-        <v/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1201.5907054634147</t>
-        </is>
-      </c>
-      <c r="J138" t="n">
-        <v/>
-      </c>
-      <c r="K138" t="n">
-        <v/>
+          <t>1075.9843902439025</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>1022.1851707317073</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>1001.7414673170732</t>
+        </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>12.282926829268293</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>0.447543</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -6132,17 +6820,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-Boiler-ELC</t>
+          <t>C_WSR-MPS-MPS-H2R</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>C_OFFC-WH</t>
+          <t>C_WSR-MPS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6152,30 +6840,38 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
-        <v/>
-      </c>
-      <c r="G139" t="n">
-        <v/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>310.17497824390244</t>
-        </is>
-      </c>
-      <c r="J139" t="n">
-        <v/>
-      </c>
-      <c r="K139" t="n">
-        <v/>
+          <t>1075.9843902439025</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>1022.1851707317073</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>1001.7414673170732</t>
+        </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -6184,7 +6880,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>0.447543</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="N139" t="n">
@@ -6200,17 +6896,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-Boiler-BIM</t>
+          <t>C_OTH-SH-Boiler-WOD</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>COMBIM</t>
+          <t>COMWOD</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>C_OFFC-WH</t>
+          <t>C_OTH-Boiler-SH</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6231,12 +6927,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>361.262496</t>
+          <t>1300.545771707317</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -6247,22 +6943,22 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>0.447543</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -6274,17 +6970,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-Boiler-H2R</t>
+          <t>C_OTH-SH-Boiler-PLT</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>COMH2R</t>
+          <t>COMPLT</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>C_OFFC-WH</t>
+          <t>C_OTH-Boiler-SH</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6294,7 +6990,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -6305,12 +7001,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>450.3740246829268</t>
+          <t>1201.5907054634147</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -6321,22 +7017,22 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>0.447543</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -6348,7 +7044,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>C_OFFC-SH-GHP-ELC</t>
+          <t>C_OTH-SH-Boiler-ELC</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6358,7 +7054,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>C_OFFC-SH</t>
+          <t>C_OTH-Boiler-SH</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6368,42 +7064,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v/>
+      </c>
+      <c r="G142" t="n">
+        <v/>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2267.428292682927</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>2154.0568780487806</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>2110.9757404878046</t>
-        </is>
+          <t>310.17497824390244</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v/>
+      </c>
+      <c r="K142" t="n">
+        <v/>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -6411,36 +7099,30 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="N142" t="n">
+        <v/>
+      </c>
+      <c r="O142" t="n">
+        <v/>
+      </c>
+      <c r="P142" t="n">
+        <v/>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>C_OFFC-WH-GHP-ELC</t>
+          <t>C_OTH-SH-Boiler-BIM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMBIM</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>C_OFFC-WH</t>
+          <t>C_OTH-Boiler-SH</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6450,57 +7132,49 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v/>
+      </c>
+      <c r="G143" t="n">
+        <v/>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2267.428292682927</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>2154.0568780487806</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>2110.9757404878046</t>
-        </is>
+          <t>361.262496</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v/>
+      </c>
+      <c r="K143" t="n">
+        <v/>
       </c>
       <c r="L143" t="inlineStr">
         <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>0.447543</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -6512,17 +7186,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>C_OFFC-MPM-MPM-ELC</t>
+          <t>C_OTH-SH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>C_OFFC-MPM</t>
+          <t>C_OTH-Boiler-SH</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6532,7 +7206,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -6543,12 +7217,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>232.01085375609756</t>
+          <t>450.3740246829268</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -6559,38 +7233,44 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N144" t="n">
-        <v/>
-      </c>
-      <c r="O144" t="n">
-        <v/>
-      </c>
-      <c r="P144" t="n">
-        <v/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>C_OFFC-MPM-MPM-H2R</t>
+          <t>C_OTH-WH-Boiler-WOD</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>COMH2R</t>
+          <t>COMWOD</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>C_OFFC-MPM</t>
+          <t>C_OTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6600,52 +7280,44 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v/>
+      </c>
+      <c r="G145" t="n">
+        <v/>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>1075.9843902439025</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>1022.1851707317073</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>1001.7414673170732</t>
-        </is>
+          <t>1300.545771707317</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v/>
+      </c>
+      <c r="K145" t="n">
+        <v/>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
+          <t>0.549133</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
           <t>0.1</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -6662,17 +7334,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>C_OFFC-MPS-MPS-H2R</t>
+          <t>C_OTH-WH-Boiler-PLT</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>COMH2R</t>
+          <t>COMPLT</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>C_OFFC-MPS</t>
+          <t>C_OTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6682,63 +7354,61 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v/>
+      </c>
+      <c r="G146" t="n">
+        <v/>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1075.9843902439025</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>1022.1851707317073</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>1001.7414673170732</t>
-        </is>
+          <t>1201.5907054634147</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v/>
+      </c>
+      <c r="K146" t="n">
+        <v/>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2.4565853658536585</t>
+          <t>12.282926829268293</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>0.447543</t>
-        </is>
-      </c>
-      <c r="N146" t="n">
-        <v/>
-      </c>
-      <c r="O146" t="n">
-        <v/>
-      </c>
-      <c r="P146" t="n">
-        <v/>
+          <t>0.549133</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>C_OFFC-SC-GHP-ELC</t>
+          <t>C_OTH-WH-Boiler-ELC</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6748,7 +7418,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>C_OFFC-SC</t>
+          <t>C_OTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6758,47 +7428,39 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v/>
+      </c>
+      <c r="G147" t="n">
+        <v/>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>1316.0284009756099</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>1250.2263053658537</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>1225.2219512195122</t>
-        </is>
+          <t>310.17497824390244</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v/>
+      </c>
+      <c r="K147" t="n">
+        <v/>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>0.223772</t>
+          <t>0.549133</t>
         </is>
       </c>
       <c r="N147" t="n">
@@ -6814,17 +7476,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>C_WSR-CK-Induction-ELC</t>
+          <t>C_OTH-WH-Boiler-BIM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMBIM</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>C_WSR-CK</t>
+          <t>C_OTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6834,7 +7496,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -6845,12 +7507,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>811.5505401951219</t>
+          <t>361.262496</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -6861,28 +7523,34 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>0.549133</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N148" t="n">
-        <v/>
-      </c>
-      <c r="O148" t="n">
-        <v/>
-      </c>
-      <c r="P148" t="n">
-        <v/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>C_WSR-CK-CK-H2R</t>
+          <t>C_OTH-WH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6892,7 +7560,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>C_WSR-CK</t>
+          <t>C_OTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6902,7 +7570,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -6913,12 +7581,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1013.3414634146342</t>
+          <t>450.3740246829268</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -6929,38 +7597,44 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
+          <t>2.4565853658536585</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>0.549133</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N149" t="n">
-        <v/>
-      </c>
-      <c r="O149" t="n">
-        <v/>
-      </c>
-      <c r="P149" t="n">
-        <v/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>C_WSR-CK-Ovens-H2R</t>
+          <t>C_OTH-WH-AirHP-ELC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>COMH2R</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>C_WSR-CK</t>
+          <t>C_OTH-WH</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6970,14 +7644,18 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v/>
-      </c>
-      <c r="G150" t="n">
-        <v/>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -6986,14 +7664,18 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>3373.710978536585</t>
-        </is>
-      </c>
-      <c r="J150" t="n">
-        <v/>
-      </c>
-      <c r="K150" t="n">
-        <v/>
+          <t>1842.439024390244</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>1750.3170731707316</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>1715.310731707317</t>
+        </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -7002,33 +7684,39 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N150" t="n">
-        <v/>
-      </c>
-      <c r="O150" t="n">
-        <v/>
-      </c>
-      <c r="P150" t="n">
-        <v/>
+          <t>0.549133</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>C_WSR-SH-Boiler-WOD</t>
+          <t>C_OTH-MPM-MPM-ELC</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>COMWOD</t>
+          <t>COMELC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>C_WSR-SH</t>
+          <t>C_OTH-MPM</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7038,7 +7726,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -7049,12 +7737,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1300.545771707317</t>
+          <t>232.01085375609756</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -7065,7 +7753,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>12.282926829268293</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -7073,36 +7761,30 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="N151" t="n">
+        <v/>
+      </c>
+      <c r="O151" t="n">
+        <v/>
+      </c>
+      <c r="P151" t="n">
+        <v/>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>C_WSR-SH-Boiler-PLT</t>
+          <t>C_OTH-MPM-MPM-H2R</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>COMPLT</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>C_WSR-SH</t>
+          <t>C_OTH-MPM</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7112,34 +7794,42 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
-        <v/>
-      </c>
-      <c r="G152" t="n">
-        <v/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1201.5907054634147</t>
-        </is>
-      </c>
-      <c r="J152" t="n">
-        <v/>
-      </c>
-      <c r="K152" t="n">
-        <v/>
+          <t>1075.9843902439025</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>1022.1851707317073</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>1001.7414673170732</t>
+        </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>12.282926829268293</t>
+          <t>2.4565853658536585</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -7147,36 +7837,30 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="N152" t="n">
+        <v/>
+      </c>
+      <c r="O152" t="n">
+        <v/>
+      </c>
+      <c r="P152" t="n">
+        <v/>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>C_WSR-SH-Boiler-ELC</t>
+          <t>C_OTH-MPS-MPS-H2R</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>COMELC</t>
+          <t>COMH2R</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>C_WSR-SH</t>
+          <t>C_OTH-MPS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7186,30 +7870,38 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v/>
-      </c>
-      <c r="G153" t="n">
-        <v/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>310.17497824390244</t>
-        </is>
-      </c>
-      <c r="J153" t="n">
-        <v/>
-      </c>
-      <c r="K153" t="n">
-        <v/>
+          <t>1075.9843902439025</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>1022.1851707317073</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>1001.7414673170732</t>
+        </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -7218,7 +7910,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.549133</t>
         </is>
       </c>
       <c r="N153" t="n">
@@ -7228,2406 +7920,6 @@
         <v/>
       </c>
       <c r="P153" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>C_WSR-SH-Boiler-BIM</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>COMBIM</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>C_WSR-SH</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="F154" t="n">
-        <v/>
-      </c>
-      <c r="G154" t="n">
-        <v/>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>361.262496</t>
-        </is>
-      </c>
-      <c r="J154" t="n">
-        <v/>
-      </c>
-      <c r="K154" t="n">
-        <v/>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>C_WSR-SH-Boiler-H2R</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>COMH2R</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>C_WSR-SH</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v/>
-      </c>
-      <c r="G155" t="n">
-        <v/>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>450.3740246829268</t>
-        </is>
-      </c>
-      <c r="J155" t="n">
-        <v/>
-      </c>
-      <c r="K155" t="n">
-        <v/>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>C_WSR-WH-Boiler-WOD</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>COMWOD</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>C_WSR-WH</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v/>
-      </c>
-      <c r="G156" t="n">
-        <v/>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1300.545771707317</t>
-        </is>
-      </c>
-      <c r="J156" t="n">
-        <v/>
-      </c>
-      <c r="K156" t="n">
-        <v/>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>12.282926829268293</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>C_WSR-WH-Boiler-PLT</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>COMPLT</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>C_WSR-WH</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v/>
-      </c>
-      <c r="G157" t="n">
-        <v/>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1201.5907054634147</t>
-        </is>
-      </c>
-      <c r="J157" t="n">
-        <v/>
-      </c>
-      <c r="K157" t="n">
-        <v/>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>12.282926829268293</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>C_WSR-WH-Boiler-ELC</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>C_WSR-WH</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="F158" t="n">
-        <v/>
-      </c>
-      <c r="G158" t="n">
-        <v/>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>310.17497824390244</t>
-        </is>
-      </c>
-      <c r="J158" t="n">
-        <v/>
-      </c>
-      <c r="K158" t="n">
-        <v/>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N158" t="n">
-        <v/>
-      </c>
-      <c r="O158" t="n">
-        <v/>
-      </c>
-      <c r="P158" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>C_WSR-WH-Boiler-BIM</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>COMBIM</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>C_WSR-WH</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="F159" t="n">
-        <v/>
-      </c>
-      <c r="G159" t="n">
-        <v/>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>361.262496</t>
-        </is>
-      </c>
-      <c r="J159" t="n">
-        <v/>
-      </c>
-      <c r="K159" t="n">
-        <v/>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>C_WSR-WH-Boiler-H2R</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>COMH2R</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>C_WSR-WH</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="F160" t="n">
-        <v/>
-      </c>
-      <c r="G160" t="n">
-        <v/>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>450.3740246829268</t>
-        </is>
-      </c>
-      <c r="J160" t="n">
-        <v/>
-      </c>
-      <c r="K160" t="n">
-        <v/>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>C_WSR-SH-GHP-ELC</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>C_WSR-SH</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>2267.428292682927</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>2154.0568780487806</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>2110.9757404878046</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>C_WSR-WH-AirHP-ELC</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>C_WSR-WH</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>1842.439024390244</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>1750.3170731707316</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>1715.310731707317</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N162" t="n">
-        <v/>
-      </c>
-      <c r="O162" t="n">
-        <v/>
-      </c>
-      <c r="P162" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>C_WSR-WH-GHP-ELC</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>C_WSR-WH</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>2267.428292682927</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>2154.0568780487806</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>2110.9757404878046</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P163" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>C_WSR-MPM-MPM-ELC</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>C_WSR-MPM</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="F164" t="n">
-        <v/>
-      </c>
-      <c r="G164" t="n">
-        <v/>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>232.01085375609756</t>
-        </is>
-      </c>
-      <c r="J164" t="n">
-        <v/>
-      </c>
-      <c r="K164" t="n">
-        <v/>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N164" t="n">
-        <v/>
-      </c>
-      <c r="O164" t="n">
-        <v/>
-      </c>
-      <c r="P164" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>C_WSR-MPM-MPM-H2R</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>COMH2R</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>C_WSR-MPM</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>1075.9843902439025</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>1022.1851707317073</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>1001.7414673170732</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="P165" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>C_WSR-MPS-MPS-H2R</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>COMH2R</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>C_WSR-MPS</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>1075.9843902439025</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>1022.1851707317073</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>1001.7414673170732</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="N166" t="n">
-        <v/>
-      </c>
-      <c r="O166" t="n">
-        <v/>
-      </c>
-      <c r="P166" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>C_WSR-SC-GHP-ELC</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>C_WSR-SC</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>1316.0284009756099</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>1250.2263053658537</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>1225.2219512195122</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>0.2415</t>
-        </is>
-      </c>
-      <c r="N167" t="n">
-        <v/>
-      </c>
-      <c r="O167" t="n">
-        <v/>
-      </c>
-      <c r="P167" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>C_OTH-SH-Boiler-WOD</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>COMWOD</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>C_OTH-SH</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="F168" t="n">
-        <v/>
-      </c>
-      <c r="G168" t="n">
-        <v/>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>1300.545771707317</t>
-        </is>
-      </c>
-      <c r="J168" t="n">
-        <v/>
-      </c>
-      <c r="K168" t="n">
-        <v/>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>12.282926829268293</t>
-        </is>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>C_OTH-SH-Boiler-PLT</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>COMPLT</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>C_OTH-SH</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="F169" t="n">
-        <v/>
-      </c>
-      <c r="G169" t="n">
-        <v/>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>1201.5907054634147</t>
-        </is>
-      </c>
-      <c r="J169" t="n">
-        <v/>
-      </c>
-      <c r="K169" t="n">
-        <v/>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>12.282926829268293</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>C_OTH-SH-Boiler-ELC</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>C_OTH-SH</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="F170" t="n">
-        <v/>
-      </c>
-      <c r="G170" t="n">
-        <v/>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>310.17497824390244</t>
-        </is>
-      </c>
-      <c r="J170" t="n">
-        <v/>
-      </c>
-      <c r="K170" t="n">
-        <v/>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N170" t="n">
-        <v/>
-      </c>
-      <c r="O170" t="n">
-        <v/>
-      </c>
-      <c r="P170" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>C_OTH-SH-Boiler-BIM</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>COMBIM</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>C_OTH-SH</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="F171" t="n">
-        <v/>
-      </c>
-      <c r="G171" t="n">
-        <v/>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>361.262496</t>
-        </is>
-      </c>
-      <c r="J171" t="n">
-        <v/>
-      </c>
-      <c r="K171" t="n">
-        <v/>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>C_OTH-SH-Boiler-H2R</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>COMH2R</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>C_OTH-SH</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="F172" t="n">
-        <v/>
-      </c>
-      <c r="G172" t="n">
-        <v/>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>450.3740246829268</t>
-        </is>
-      </c>
-      <c r="J172" t="n">
-        <v/>
-      </c>
-      <c r="K172" t="n">
-        <v/>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>C_OTH-WH-Boiler-WOD</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>COMWOD</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>C_OTH-WH</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="F173" t="n">
-        <v/>
-      </c>
-      <c r="G173" t="n">
-        <v/>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>1300.545771707317</t>
-        </is>
-      </c>
-      <c r="J173" t="n">
-        <v/>
-      </c>
-      <c r="K173" t="n">
-        <v/>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>12.282926829268293</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>0.549133</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>C_OTH-WH-Boiler-PLT</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>COMPLT</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>C_OTH-WH</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="F174" t="n">
-        <v/>
-      </c>
-      <c r="G174" t="n">
-        <v/>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>1201.5907054634147</t>
-        </is>
-      </c>
-      <c r="J174" t="n">
-        <v/>
-      </c>
-      <c r="K174" t="n">
-        <v/>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>12.282926829268293</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>0.549133</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>C_OTH-WH-Boiler-ELC</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>C_OTH-WH</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="F175" t="n">
-        <v/>
-      </c>
-      <c r="G175" t="n">
-        <v/>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>310.17497824390244</t>
-        </is>
-      </c>
-      <c r="J175" t="n">
-        <v/>
-      </c>
-      <c r="K175" t="n">
-        <v/>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>0.549133</t>
-        </is>
-      </c>
-      <c r="N175" t="n">
-        <v/>
-      </c>
-      <c r="O175" t="n">
-        <v/>
-      </c>
-      <c r="P175" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>C_OTH-WH-Boiler-BIM</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>COMBIM</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>C_OTH-WH</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="F176" t="n">
-        <v/>
-      </c>
-      <c r="G176" t="n">
-        <v/>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>361.262496</t>
-        </is>
-      </c>
-      <c r="J176" t="n">
-        <v/>
-      </c>
-      <c r="K176" t="n">
-        <v/>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>0.549133</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>C_OTH-WH-Boiler-H2R</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>COMH2R</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>C_OTH-WH</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="F177" t="n">
-        <v/>
-      </c>
-      <c r="G177" t="n">
-        <v/>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>450.3740246829268</t>
-        </is>
-      </c>
-      <c r="J177" t="n">
-        <v/>
-      </c>
-      <c r="K177" t="n">
-        <v/>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>0.549133</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>C_OTH-SH-GHP-ELC</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>C_OTH-SH</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>2267.428292682927</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>2154.0568780487806</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>2110.9757404878046</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>C_OTH-WH-AirHP-ELC</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>C_OTH-WH</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>1842.439024390244</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>1750.3170731707316</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>1715.310731707317</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>0.549133</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>C_OTH-WH-GHP-ELC</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>C_OTH-WH</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>2267.428292682927</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>2154.0568780487806</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>2110.9757404878046</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>0.549133</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>C_OTH-MPM-MPM-ELC</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>C_OTH-MPM</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="F181" t="n">
-        <v/>
-      </c>
-      <c r="G181" t="n">
-        <v/>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>232.01085375609756</t>
-        </is>
-      </c>
-      <c r="J181" t="n">
-        <v/>
-      </c>
-      <c r="K181" t="n">
-        <v/>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N181" t="n">
-        <v/>
-      </c>
-      <c r="O181" t="n">
-        <v/>
-      </c>
-      <c r="P181" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>C_OTH-MPM-MPM-H2R</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>COMH2R</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>C_OTH-MPM</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>1075.9843902439025</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>1022.1851707317073</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>1001.7414673170732</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N182" t="n">
-        <v/>
-      </c>
-      <c r="O182" t="n">
-        <v/>
-      </c>
-      <c r="P182" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>C_OTH-MPS-MPS-H2R</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>COMH2R</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>C_OTH-MPS</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>1075.9843902439025</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>1022.1851707317073</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>1001.7414673170732</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>2.4565853658536585</t>
-        </is>
-      </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>0.549133</t>
-        </is>
-      </c>
-      <c r="N183" t="n">
-        <v/>
-      </c>
-      <c r="O183" t="n">
-        <v/>
-      </c>
-      <c r="P183" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>C_OTH-SC-GHP-ELC</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>C_OTH-SC</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>1316.0284009756099</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>1250.2263053658537</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>1225.2219512195122</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>0.108447</t>
-        </is>
-      </c>
-      <c r="N184" t="n">
-        <v/>
-      </c>
-      <c r="O184" t="n">
-        <v/>
-      </c>
-      <c r="P184" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>C_DATA-SC-GHP-ELC</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>COMELC</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>C_DATA-SC</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>1316.0284009756099</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>1250.2263053658537</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>1225.2219512195122</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>0.223772</t>
-        </is>
-      </c>
-      <c r="N185" t="n">
-        <v/>
-      </c>
-      <c r="O185" t="n">
-        <v/>
-      </c>
-      <c r="P185" t="n">
         <v/>
       </c>
     </row>
